--- a/data/macro/South Korea/Export.xlsx
+++ b/data/macro/South Korea/Export.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76664FC-C6C3-4749-A8B5-9F89D980AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CDDFD2-610B-4FAC-A946-AB41B59DCFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
   </bookViews>
   <sheets>
-    <sheet name="KR Export" sheetId="1" r:id="rId1"/>
+    <sheet name="KOEXTOTY" sheetId="1" r:id="rId1"/>
     <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -72,7 +72,6 @@
   </si>
   <si>
     <t>https://kr.investing.com/economic-calendar/south-korean-export-growth-1316</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -80,12 +79,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -159,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -176,43 +175,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3">
